--- a/Excel/new_jobs(flags).xlsx
+++ b/Excel/new_jobs(flags).xlsx
@@ -559,7 +559,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="n">
-        <v>1101100</v>
+        <v>1100001</v>
       </c>
     </row>
     <row r="3">
@@ -621,7 +621,7 @@
         <v>1</v>
       </c>
       <c r="N3" t="n">
-        <v>1100101</v>
+        <v>1001001.1</v>
       </c>
     </row>
     <row r="4">
@@ -683,7 +683,7 @@
         <v>1</v>
       </c>
       <c r="N4" t="n">
-        <v>1100101</v>
+        <v>1000001.1</v>
       </c>
     </row>
     <row r="5">
@@ -745,7 +745,7 @@
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="6">
@@ -807,7 +807,7 @@
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>100000</v>
+        <v>1001000</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>100000</v>
+        <v>1001000</v>
       </c>
     </row>
     <row r="8">
@@ -931,7 +931,7 @@
         <v>1</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="9">
@@ -993,7 +993,7 @@
         <v>1</v>
       </c>
       <c r="N9" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1055,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="11">
@@ -1117,7 +1117,7 @@
         <v>1</v>
       </c>
       <c r="N11" t="n">
-        <v>100100</v>
+        <v>1000001.01</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="N12" t="n">
-        <v>100000</v>
+        <v>1000000.01</v>
       </c>
     </row>
     <row r="13">
@@ -1241,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="N13" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="14">
@@ -1303,7 +1303,7 @@
         <v>1</v>
       </c>
       <c r="N14" t="n">
-        <v>101100</v>
+        <v>1100001.01</v>
       </c>
     </row>
     <row r="15">
@@ -1365,7 +1365,7 @@
         <v>1</v>
       </c>
       <c r="N15" t="n">
-        <v>2000000</v>
+        <v>10001000</v>
       </c>
     </row>
     <row r="16">
@@ -1489,7 +1489,7 @@
         <v>1</v>
       </c>
       <c r="N17" t="n">
-        <v>100111</v>
+        <v>1000101.1</v>
       </c>
     </row>
     <row r="18">
@@ -1646,7 +1646,7 @@
         <v>1</v>
       </c>
       <c r="N19" t="n">
-        <v>2101100</v>
+        <v>11100001</v>
       </c>
     </row>
     <row r="20">
@@ -1740,7 +1740,7 @@
         <v>1</v>
       </c>
       <c r="N20" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="21">
@@ -1830,7 +1830,7 @@
         <v>1</v>
       </c>
       <c r="N21" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="22">
@@ -1892,7 +1892,7 @@
         <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>10000000</v>
+        <v>100001000</v>
       </c>
     </row>
     <row r="23">
@@ -1950,7 +1950,7 @@
         <v>1</v>
       </c>
       <c r="N23" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2004,7 +2004,7 @@
         <v>1</v>
       </c>
       <c r="N24" t="n">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="25">
@@ -2101,7 +2101,7 @@
         <v>1</v>
       </c>
       <c r="N25" t="n">
-        <v>100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="26">
@@ -2159,7 +2159,7 @@
         <v>1</v>
       </c>
       <c r="N26" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2221,7 +2221,7 @@
         <v>1</v>
       </c>
       <c r="N27" t="n">
-        <v>1100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="28">
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>12100100</v>
+        <v>111001001</v>
       </c>
     </row>
     <row r="29">
@@ -2458,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>1100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="30">
@@ -2620,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2721,7 +2721,7 @@
         <v>1</v>
       </c>
       <c r="N32" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="33">
@@ -2783,7 +2783,7 @@
         <v>1</v>
       </c>
       <c r="N33" t="n">
-        <v>2100100</v>
+        <v>11010001</v>
       </c>
     </row>
     <row r="34">
@@ -2845,7 +2845,7 @@
         <v>1</v>
       </c>
       <c r="N34" t="n">
-        <v>2100100</v>
+        <v>11010001</v>
       </c>
     </row>
     <row r="35">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>10000100</v>
+        <v>100000001</v>
       </c>
     </row>
     <row r="36">
@@ -3011,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="N36" t="n">
-        <v>11000100</v>
+        <v>100001001</v>
       </c>
     </row>
     <row r="37">
@@ -3073,7 +3073,7 @@
         <v>1</v>
       </c>
       <c r="N37" t="n">
-        <v>11000000</v>
+        <v>100001000</v>
       </c>
     </row>
     <row r="38">
@@ -3176,7 +3176,7 @@
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1000100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -3281,7 +3281,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -3383,7 +3383,7 @@
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1000100</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="41">
@@ -3486,7 +3486,7 @@
         <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>1000100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -3591,7 +3591,7 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3696,7 +3696,7 @@
         <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -3799,7 +3799,7 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>1000100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -3900,7 +3900,7 @@
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1000100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3962,7 +3962,7 @@
         <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>11101101</v>
+        <v>101100001.11</v>
       </c>
     </row>
     <row r="47">
@@ -4024,7 +4024,7 @@
         <v>1</v>
       </c>
       <c r="N47" t="n">
-        <v>1100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="48">
@@ -4103,7 +4103,7 @@
         <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>1100100</v>
+        <v>1000001.01</v>
       </c>
     </row>
     <row r="49">
@@ -4184,7 +4184,7 @@
         <v>1</v>
       </c>
       <c r="N49" t="n">
-        <v>1100101</v>
+        <v>1001001.11</v>
       </c>
     </row>
     <row r="50">
@@ -4302,7 +4302,7 @@
         <v>1</v>
       </c>
       <c r="N50" t="n">
-        <v>11100100</v>
+        <v>101000001</v>
       </c>
     </row>
     <row r="51">
@@ -4403,7 +4403,7 @@
         <v>1</v>
       </c>
       <c r="N51" t="n">
-        <v>2101100</v>
+        <v>11100001</v>
       </c>
     </row>
     <row r="52">
@@ -4519,7 +4519,7 @@
         <v>1</v>
       </c>
       <c r="N53" t="n">
-        <v>3000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="54">
@@ -4577,7 +4577,7 @@
         <v>1</v>
       </c>
       <c r="N54" t="n">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="55">
@@ -4697,7 +4697,7 @@
         <v>0</v>
       </c>
       <c r="N56" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -4759,7 +4759,7 @@
         <v>1</v>
       </c>
       <c r="N57" t="n">
-        <v>100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="58">
@@ -4821,7 +4821,7 @@
         <v>1</v>
       </c>
       <c r="N58" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -4883,7 +4883,7 @@
         <v>1</v>
       </c>
       <c r="N59" t="n">
-        <v>100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="60">
@@ -5007,7 +5007,7 @@
         <v>1</v>
       </c>
       <c r="N61" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="62">
@@ -5069,7 +5069,7 @@
         <v>1</v>
       </c>
       <c r="N62" t="n">
-        <v>1100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="63">
@@ -5131,7 +5131,7 @@
         <v>1</v>
       </c>
       <c r="N63" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="64">
@@ -5193,7 +5193,7 @@
         <v>1</v>
       </c>
       <c r="N64" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="65">
@@ -5255,7 +5255,7 @@
         <v>1</v>
       </c>
       <c r="N65" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="66">
@@ -5317,7 +5317,7 @@
         <v>1</v>
       </c>
       <c r="N66" t="n">
-        <v>101100</v>
+        <v>1101001</v>
       </c>
     </row>
     <row r="67">
@@ -5441,7 +5441,7 @@
         <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>1100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="69">
@@ -5503,7 +5503,7 @@
         <v>1</v>
       </c>
       <c r="N69" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="70">
@@ -5565,7 +5565,7 @@
         <v>0</v>
       </c>
       <c r="N70" t="n">
-        <v>100100</v>
+        <v>1010001</v>
       </c>
     </row>
     <row r="71">
@@ -5627,7 +5627,7 @@
         <v>1</v>
       </c>
       <c r="N71" t="n">
-        <v>1100001</v>
+        <v>1000000.1</v>
       </c>
     </row>
     <row r="72">
@@ -5689,7 +5689,7 @@
         <v>1</v>
       </c>
       <c r="N72" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="73">
@@ -5751,7 +5751,7 @@
         <v>1</v>
       </c>
       <c r="N73" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="74">
@@ -5813,7 +5813,7 @@
         <v>1</v>
       </c>
       <c r="N74" t="n">
-        <v>100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="75">
@@ -5875,7 +5875,7 @@
         <v>1</v>
       </c>
       <c r="N75" t="n">
-        <v>101100</v>
+        <v>1101001</v>
       </c>
     </row>
     <row r="76">
@@ -5937,7 +5937,7 @@
         <v>1</v>
       </c>
       <c r="N76" t="n">
-        <v>1000100</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -5999,7 +5999,7 @@
         <v>0</v>
       </c>
       <c r="N77" t="n">
-        <v>1100101</v>
+        <v>1000001.11</v>
       </c>
     </row>
     <row r="78">
@@ -6061,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>1100101</v>
+        <v>1000001.11</v>
       </c>
     </row>
     <row r="79">
@@ -6123,7 +6123,7 @@
         <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>1100101</v>
+        <v>1000001.11</v>
       </c>
     </row>
     <row r="80">
@@ -6185,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="N80" t="n">
-        <v>2100101</v>
+        <v>11000001.11</v>
       </c>
     </row>
     <row r="81">
@@ -6247,7 +6247,7 @@
         <v>1</v>
       </c>
       <c r="N81" t="n">
-        <v>2100101</v>
+        <v>11000001.11</v>
       </c>
     </row>
     <row r="82">
@@ -6309,7 +6309,7 @@
         <v>0</v>
       </c>
       <c r="N82" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="83">
@@ -6371,7 +6371,7 @@
         <v>1</v>
       </c>
       <c r="N83" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="84">
@@ -6433,7 +6433,7 @@
         <v>0</v>
       </c>
       <c r="N84" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="85">
@@ -6495,7 +6495,7 @@
         <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>2100100</v>
+        <v>11010001</v>
       </c>
     </row>
     <row r="86">
@@ -6557,7 +6557,7 @@
         <v>1</v>
       </c>
       <c r="N86" t="n">
-        <v>2100100</v>
+        <v>11010001</v>
       </c>
     </row>
     <row r="87">
@@ -6619,7 +6619,7 @@
         <v>0</v>
       </c>
       <c r="N87" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="88">
@@ -6681,7 +6681,7 @@
         <v>1</v>
       </c>
       <c r="N88" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="89">
@@ -6743,7 +6743,7 @@
         <v>1</v>
       </c>
       <c r="N89" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="90">
@@ -6805,7 +6805,7 @@
         <v>0</v>
       </c>
       <c r="N90" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="91">
@@ -6867,7 +6867,7 @@
         <v>1</v>
       </c>
       <c r="N91" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="92">
@@ -6929,7 +6929,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="93">
@@ -6991,7 +6991,7 @@
         <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>100100</v>
+        <v>1001001.01</v>
       </c>
     </row>
     <row r="94">
@@ -7053,7 +7053,7 @@
         <v>1</v>
       </c>
       <c r="N94" t="n">
-        <v>100100</v>
+        <v>1001001.01</v>
       </c>
     </row>
     <row r="95">
@@ -7239,7 +7239,7 @@
         <v>0</v>
       </c>
       <c r="N97" t="n">
-        <v>100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="98">
@@ -7301,7 +7301,7 @@
         <v>1</v>
       </c>
       <c r="N98" t="n">
-        <v>10000000</v>
+        <v>100001000</v>
       </c>
     </row>
     <row r="99">
@@ -7363,7 +7363,7 @@
         <v>1</v>
       </c>
       <c r="N99" t="n">
-        <v>10000000</v>
+        <v>100001000</v>
       </c>
     </row>
     <row r="100">
@@ -7425,7 +7425,7 @@
         <v>1</v>
       </c>
       <c r="N100" t="n">
-        <v>11100100</v>
+        <v>101001001</v>
       </c>
     </row>
     <row r="101">
@@ -7487,7 +7487,7 @@
         <v>1</v>
       </c>
       <c r="N101" t="n">
-        <v>11100111</v>
+        <v>101001101.1</v>
       </c>
     </row>
     <row r="102">
@@ -7549,7 +7549,7 @@
         <v>0</v>
       </c>
       <c r="N102" t="n">
-        <v>1100111</v>
+        <v>1001101.1</v>
       </c>
     </row>
     <row r="103">
@@ -7611,7 +7611,7 @@
         <v>1</v>
       </c>
       <c r="N103" t="n">
-        <v>11101100</v>
+        <v>101101001</v>
       </c>
     </row>
     <row r="104">
@@ -7673,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="N104" t="n">
-        <v>1000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105">
@@ -7735,7 +7735,7 @@
         <v>0</v>
       </c>
       <c r="N105" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="106">
@@ -7797,7 +7797,7 @@
         <v>1</v>
       </c>
       <c r="N106" t="n">
-        <v>11100100</v>
+        <v>101001001</v>
       </c>
     </row>
     <row r="107">
@@ -7859,7 +7859,7 @@
         <v>0</v>
       </c>
       <c r="N107" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="108">
@@ -7921,7 +7921,7 @@
         <v>1</v>
       </c>
       <c r="N108" t="n">
-        <v>11100100</v>
+        <v>101001001</v>
       </c>
     </row>
     <row r="109">
@@ -7983,7 +7983,7 @@
         <v>0</v>
       </c>
       <c r="N109" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="110">
@@ -8045,7 +8045,7 @@
         <v>1</v>
       </c>
       <c r="N110" t="n">
-        <v>11100100</v>
+        <v>101001001</v>
       </c>
     </row>
     <row r="111">
@@ -8107,7 +8107,7 @@
         <v>0</v>
       </c>
       <c r="N111" t="n">
-        <v>1101100</v>
+        <v>1101001</v>
       </c>
     </row>
     <row r="112">
@@ -8169,7 +8169,7 @@
         <v>1</v>
       </c>
       <c r="N112" t="n">
-        <v>11101100</v>
+        <v>101101001</v>
       </c>
     </row>
     <row r="113">
@@ -8231,7 +8231,7 @@
         <v>1</v>
       </c>
       <c r="N113" t="n">
-        <v>11100100</v>
+        <v>101001001</v>
       </c>
     </row>
     <row r="114">
@@ -8293,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="115">
@@ -8355,7 +8355,7 @@
         <v>1</v>
       </c>
       <c r="N115" t="n">
-        <v>10000001</v>
+        <v>100000000.1</v>
       </c>
     </row>
     <row r="116">
@@ -8417,7 +8417,7 @@
         <v>1</v>
       </c>
       <c r="N116" t="n">
-        <v>1100101</v>
+        <v>1000001.1</v>
       </c>
     </row>
     <row r="117">
@@ -8479,7 +8479,7 @@
         <v>1</v>
       </c>
       <c r="N117" t="n">
-        <v>100100</v>
+        <v>1000001.01</v>
       </c>
     </row>
     <row r="118">
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="N118" t="n">
-        <v>2000000</v>
+        <v>10000000</v>
       </c>
     </row>
     <row r="119">
@@ -8603,7 +8603,7 @@
         <v>1</v>
       </c>
       <c r="N119" t="n">
-        <v>1101101</v>
+        <v>1110001.11</v>
       </c>
     </row>
     <row r="120">
@@ -8665,7 +8665,7 @@
         <v>0</v>
       </c>
       <c r="N120" t="n">
-        <v>1101101</v>
+        <v>1101001.11</v>
       </c>
     </row>
     <row r="121">
@@ -8727,7 +8727,7 @@
         <v>0</v>
       </c>
       <c r="N121" t="n">
-        <v>1101101</v>
+        <v>1110001.11</v>
       </c>
     </row>
     <row r="122">
@@ -8789,7 +8789,7 @@
         <v>1</v>
       </c>
       <c r="N122" t="n">
-        <v>1101101</v>
+        <v>1101001.11</v>
       </c>
     </row>
     <row r="123">
@@ -8851,7 +8851,7 @@
         <v>1</v>
       </c>
       <c r="N123" t="n">
-        <v>1101101</v>
+        <v>1110001.11</v>
       </c>
     </row>
     <row r="124">
@@ -8913,7 +8913,7 @@
         <v>1</v>
       </c>
       <c r="N124" t="n">
-        <v>2101100</v>
+        <v>11101001.01</v>
       </c>
     </row>
     <row r="125">
@@ -8975,7 +8975,7 @@
         <v>1</v>
       </c>
       <c r="N125" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="126">
@@ -9037,7 +9037,7 @@
         <v>1</v>
       </c>
       <c r="N126" t="n">
-        <v>1000000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="127">
@@ -9099,7 +9099,7 @@
         <v>1</v>
       </c>
       <c r="N127" t="n">
-        <v>1100000</v>
+        <v>1001000</v>
       </c>
     </row>
     <row r="128">
@@ -9161,7 +9161,7 @@
         <v>1</v>
       </c>
       <c r="N128" t="n">
-        <v>1100000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="129">
@@ -9223,7 +9223,7 @@
         <v>1</v>
       </c>
       <c r="N129" t="n">
-        <v>1101100</v>
+        <v>1101001</v>
       </c>
     </row>
     <row r="130">
@@ -9285,7 +9285,7 @@
         <v>1</v>
       </c>
       <c r="N130" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="131">
@@ -9347,7 +9347,7 @@
         <v>1</v>
       </c>
       <c r="N131" t="n">
-        <v>1101100</v>
+        <v>1101001</v>
       </c>
     </row>
     <row r="132">
@@ -9409,7 +9409,7 @@
         <v>1</v>
       </c>
       <c r="N132" t="n">
-        <v>1100101</v>
+        <v>1001001.1</v>
       </c>
     </row>
     <row r="133">
@@ -9471,7 +9471,7 @@
         <v>1</v>
       </c>
       <c r="N133" t="n">
-        <v>1000101</v>
+        <v>1001.1</v>
       </c>
     </row>
     <row r="134">
@@ -9533,7 +9533,7 @@
         <v>1</v>
       </c>
       <c r="N134" t="n">
-        <v>1100101</v>
+        <v>1001001.1</v>
       </c>
     </row>
     <row r="135">
@@ -9595,7 +9595,7 @@
         <v>1</v>
       </c>
       <c r="N135" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="136">
@@ -9657,7 +9657,7 @@
         <v>1</v>
       </c>
       <c r="N136" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="137">
@@ -9719,7 +9719,7 @@
         <v>1</v>
       </c>
       <c r="N137" t="n">
-        <v>1100101</v>
+        <v>1001001.1</v>
       </c>
     </row>
     <row r="138">
@@ -9781,7 +9781,7 @@
         <v>1</v>
       </c>
       <c r="N138" t="n">
-        <v>100000</v>
+        <v>1001000</v>
       </c>
     </row>
     <row r="139">
@@ -9843,7 +9843,7 @@
         <v>1</v>
       </c>
       <c r="N139" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="140">
@@ -9905,7 +9905,7 @@
         <v>1</v>
       </c>
       <c r="N140" t="n">
-        <v>2100100</v>
+        <v>11001001</v>
       </c>
     </row>
     <row r="141">
@@ -9967,7 +9967,7 @@
         <v>1</v>
       </c>
       <c r="N141" t="n">
-        <v>1100000</v>
+        <v>1001000</v>
       </c>
     </row>
     <row r="142">
@@ -10029,7 +10029,7 @@
         <v>1</v>
       </c>
       <c r="N142" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="143">
@@ -10091,7 +10091,7 @@
         <v>1</v>
       </c>
       <c r="N143" t="n">
-        <v>1101101</v>
+        <v>1110001.1</v>
       </c>
     </row>
     <row r="144">
@@ -10153,7 +10153,7 @@
         <v>1</v>
       </c>
       <c r="N144" t="n">
-        <v>2100100</v>
+        <v>11001001</v>
       </c>
     </row>
     <row r="145">
@@ -10215,7 +10215,7 @@
         <v>1</v>
       </c>
       <c r="N145" t="n">
-        <v>100000</v>
+        <v>1001000</v>
       </c>
     </row>
     <row r="146">
@@ -10277,7 +10277,7 @@
         <v>1</v>
       </c>
       <c r="N146" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="147">
@@ -10339,7 +10339,7 @@
         <v>1</v>
       </c>
       <c r="N147" t="n">
-        <v>100100</v>
+        <v>1001001.01</v>
       </c>
     </row>
     <row r="148">
@@ -10401,7 +10401,7 @@
         <v>1</v>
       </c>
       <c r="N148" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="149">
@@ -10463,7 +10463,7 @@
         <v>0</v>
       </c>
       <c r="N149" t="n">
-        <v>100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="150">
@@ -10525,7 +10525,7 @@
         <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="151">
@@ -10587,7 +10587,7 @@
         <v>1</v>
       </c>
       <c r="N151" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="152">
@@ -10649,7 +10649,7 @@
         <v>1</v>
       </c>
       <c r="N152" t="n">
-        <v>100100</v>
+        <v>1000001.01</v>
       </c>
     </row>
     <row r="153">
@@ -10711,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="N153" t="n">
-        <v>100100</v>
+        <v>1000001.01</v>
       </c>
     </row>
     <row r="154">
@@ -10773,7 +10773,7 @@
         <v>0</v>
       </c>
       <c r="N154" t="n">
-        <v>100101</v>
+        <v>1001001.1</v>
       </c>
     </row>
     <row r="155">
@@ -10835,7 +10835,7 @@
         <v>1</v>
       </c>
       <c r="N155" t="n">
-        <v>100101</v>
+        <v>1001001.1</v>
       </c>
     </row>
     <row r="156">
@@ -10897,7 +10897,7 @@
         <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>100101</v>
+        <v>1000001.1</v>
       </c>
     </row>
     <row r="157">
@@ -10959,7 +10959,7 @@
         <v>1</v>
       </c>
       <c r="N157" t="n">
-        <v>100101</v>
+        <v>1000001.1</v>
       </c>
     </row>
     <row r="158">
@@ -11021,7 +11021,7 @@
         <v>1</v>
       </c>
       <c r="N158" t="n">
-        <v>11100100</v>
+        <v>101001001</v>
       </c>
     </row>
     <row r="159">
@@ -11083,7 +11083,7 @@
         <v>1</v>
       </c>
       <c r="N159" t="n">
-        <v>10100100</v>
+        <v>101000001</v>
       </c>
     </row>
     <row r="160">
@@ -11207,7 +11207,7 @@
         <v>1</v>
       </c>
       <c r="N161" t="n">
-        <v>11100100</v>
+        <v>101001001</v>
       </c>
     </row>
     <row r="162">
@@ -11309,7 +11309,7 @@
         <v>1</v>
       </c>
       <c r="N162" t="n">
-        <v>1100000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="163">
@@ -11371,7 +11371,7 @@
         <v>1</v>
       </c>
       <c r="N163" t="n">
-        <v>2100100</v>
+        <v>11000001.01</v>
       </c>
     </row>
     <row r="164">
@@ -11433,7 +11433,7 @@
         <v>1</v>
       </c>
       <c r="N164" t="n">
-        <v>2100100</v>
+        <v>11000001.01</v>
       </c>
     </row>
     <row r="165">
@@ -11495,7 +11495,7 @@
         <v>1</v>
       </c>
       <c r="N165" t="n">
-        <v>2100100</v>
+        <v>11001001.01</v>
       </c>
     </row>
     <row r="166">
@@ -11557,7 +11557,7 @@
         <v>1</v>
       </c>
       <c r="N166" t="n">
-        <v>2100100</v>
+        <v>11001001.01</v>
       </c>
     </row>
     <row r="167">
@@ -11619,7 +11619,7 @@
         <v>1</v>
       </c>
       <c r="N167" t="n">
-        <v>1101100</v>
+        <v>1101001</v>
       </c>
     </row>
     <row r="168">
@@ -11708,7 +11708,7 @@
         <v>1</v>
       </c>
       <c r="N168" t="n">
-        <v>11000001</v>
+        <v>100001000.1</v>
       </c>
     </row>
     <row r="169">
@@ -11831,7 +11831,7 @@
         <v>1</v>
       </c>
       <c r="N169" t="n">
-        <v>11100000</v>
+        <v>101000000</v>
       </c>
     </row>
     <row r="170">
@@ -11957,7 +11957,7 @@
         <v>1</v>
       </c>
       <c r="N170" t="n">
-        <v>10000000</v>
+        <v>100001000</v>
       </c>
     </row>
     <row r="171">
@@ -12076,7 +12076,7 @@
         <v>1</v>
       </c>
       <c r="N171" t="n">
-        <v>11101100</v>
+        <v>101101001</v>
       </c>
     </row>
     <row r="172">
@@ -12198,7 +12198,7 @@
         <v>1</v>
       </c>
       <c r="N172" t="n">
-        <v>11100100</v>
+        <v>101001001</v>
       </c>
     </row>
     <row r="173">
@@ -12277,7 +12277,7 @@
         <v>1</v>
       </c>
       <c r="N173" t="n">
-        <v>2100000</v>
+        <v>11000000</v>
       </c>
     </row>
     <row r="174">
@@ -12339,7 +12339,7 @@
         <v>1</v>
       </c>
       <c r="N174" t="n">
-        <v>10100000</v>
+        <v>101001000</v>
       </c>
     </row>
     <row r="175">
@@ -12439,7 +12439,7 @@
         <v>1</v>
       </c>
       <c r="N175" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="176">
@@ -12501,7 +12501,7 @@
         <v>1</v>
       </c>
       <c r="N176" t="n">
-        <v>10100000</v>
+        <v>101000000</v>
       </c>
     </row>
     <row r="177">
@@ -12563,7 +12563,7 @@
         <v>1</v>
       </c>
       <c r="N177" t="n">
-        <v>2000011</v>
+        <v>10001100.1</v>
       </c>
     </row>
     <row r="178">
@@ -12625,7 +12625,7 @@
         <v>1</v>
       </c>
       <c r="N178" t="n">
-        <v>1100101</v>
+        <v>1001001.1</v>
       </c>
     </row>
     <row r="179">
@@ -12687,7 +12687,7 @@
         <v>1</v>
       </c>
       <c r="N179" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="180">
@@ -12749,7 +12749,7 @@
         <v>1</v>
       </c>
       <c r="N180" t="n">
-        <v>100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="181">
@@ -12811,7 +12811,7 @@
         <v>1</v>
       </c>
       <c r="N181" t="n">
-        <v>100100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="182">
@@ -12873,7 +12873,7 @@
         <v>1</v>
       </c>
       <c r="N182" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="183">
@@ -12935,7 +12935,7 @@
         <v>1</v>
       </c>
       <c r="N183" t="n">
-        <v>1101101</v>
+        <v>1100001.11</v>
       </c>
     </row>
     <row r="184">
@@ -12997,7 +12997,7 @@
         <v>1</v>
       </c>
       <c r="N184" t="n">
-        <v>1000001</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="185">
@@ -13121,7 +13121,7 @@
         <v>1</v>
       </c>
       <c r="N186" t="n">
-        <v>1101101</v>
+        <v>1100001.11</v>
       </c>
     </row>
     <row r="187">
@@ -13183,7 +13183,7 @@
         <v>1</v>
       </c>
       <c r="N187" t="n">
-        <v>2100100</v>
+        <v>11000001</v>
       </c>
     </row>
     <row r="188">
@@ -13245,7 +13245,7 @@
         <v>1</v>
       </c>
       <c r="N188" t="n">
-        <v>1101100</v>
+        <v>1100001</v>
       </c>
     </row>
     <row r="189">
@@ -13307,7 +13307,7 @@
         <v>1</v>
       </c>
       <c r="N189" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="190">
@@ -13431,7 +13431,7 @@
         <v>1</v>
       </c>
       <c r="N191" t="n">
-        <v>10000100</v>
+        <v>100000001</v>
       </c>
     </row>
     <row r="192">
@@ -13597,7 +13597,7 @@
         <v>1</v>
       </c>
       <c r="N192" t="n">
-        <v>10100000</v>
+        <v>101000000</v>
       </c>
     </row>
     <row r="193">
@@ -13708,7 +13708,7 @@
         <v>1</v>
       </c>
       <c r="N193" t="n">
-        <v>12101100</v>
+        <v>111100001</v>
       </c>
     </row>
     <row r="194">
@@ -13770,7 +13770,7 @@
         <v>1</v>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="195">
@@ -13832,7 +13832,7 @@
         <v>1</v>
       </c>
       <c r="N195" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="196">
@@ -13894,7 +13894,7 @@
         <v>1</v>
       </c>
       <c r="N196" t="n">
-        <v>100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="197">
@@ -13956,7 +13956,7 @@
         <v>1</v>
       </c>
       <c r="N197" t="n">
-        <v>1100100</v>
+        <v>1001001</v>
       </c>
     </row>
     <row r="198">
@@ -14018,7 +14018,7 @@
         <v>1</v>
       </c>
       <c r="N198" t="n">
-        <v>101000</v>
+        <v>1100000</v>
       </c>
     </row>
     <row r="199">
@@ -14080,7 +14080,7 @@
         <v>1</v>
       </c>
       <c r="N199" t="n">
-        <v>11100101</v>
+        <v>101001001.11</v>
       </c>
     </row>
     <row r="200">
@@ -14204,7 +14204,7 @@
         <v>1</v>
       </c>
       <c r="N201" t="n">
-        <v>12101100</v>
+        <v>111100001</v>
       </c>
     </row>
     <row r="202">
@@ -14266,7 +14266,7 @@
         <v>1</v>
       </c>
       <c r="N202" t="n">
-        <v>100000</v>
+        <v>1000000</v>
       </c>
     </row>
     <row r="203">
@@ -14390,7 +14390,7 @@
         <v>1</v>
       </c>
       <c r="N204" t="n">
-        <v>1000100</v>
+        <v>1000001</v>
       </c>
     </row>
     <row r="205">
@@ -14452,7 +14452,7 @@
         <v>1</v>
       </c>
       <c r="N205" t="n">
-        <v>10100100</v>
+        <v>101001001.01</v>
       </c>
     </row>
     <row r="206">
@@ -14514,7 +14514,7 @@
         <v>1</v>
       </c>
       <c r="N206" t="n">
-        <v>11101100</v>
+        <v>101100001.01</v>
       </c>
     </row>
     <row r="207">
@@ -14576,7 +14576,7 @@
         <v>1</v>
       </c>
       <c r="N207" t="n">
-        <v>11000100</v>
+        <v>100000001</v>
       </c>
     </row>
     <row r="208">
@@ -14638,7 +14638,7 @@
         <v>1</v>
       </c>
       <c r="N208" t="n">
-        <v>11000100</v>
+        <v>100000001</v>
       </c>
     </row>
     <row r="209">
@@ -14700,7 +14700,7 @@
         <v>1</v>
       </c>
       <c r="N209" t="n">
-        <v>10100101</v>
+        <v>101001001.1</v>
       </c>
     </row>
     <row r="210">
@@ -14762,7 +14762,7 @@
         <v>1</v>
       </c>
       <c r="N210" t="n">
-        <v>12101100</v>
+        <v>111101001</v>
       </c>
     </row>
     <row r="211">
@@ -14824,7 +14824,7 @@
         <v>1</v>
       </c>
       <c r="N211" t="n">
-        <v>12101100</v>
+        <v>111101001</v>
       </c>
     </row>
     <row r="212">
@@ -14886,7 +14886,7 @@
         <v>1</v>
       </c>
       <c r="N212" t="n">
-        <v>12101100</v>
+        <v>111101001</v>
       </c>
     </row>
     <row r="213">
@@ -14948,7 +14948,7 @@
         <v>1</v>
       </c>
       <c r="N213" t="n">
-        <v>10000100</v>
+        <v>100000001</v>
       </c>
     </row>
     <row r="214">
@@ -15010,7 +15010,7 @@
         <v>1</v>
       </c>
       <c r="N214" t="n">
-        <v>1100101</v>
+        <v>1001001.1</v>
       </c>
     </row>
     <row r="215">
@@ -15072,7 +15072,7 @@
         <v>1</v>
       </c>
       <c r="N215" t="n">
-        <v>100100</v>
+        <v>1001001.01</v>
       </c>
     </row>
     <row r="216">
@@ -15134,7 +15134,7 @@
         <v>1</v>
       </c>
       <c r="N216" t="n">
-        <v>100100</v>
+        <v>1001001.01</v>
       </c>
     </row>
     <row r="217">
@@ -15258,7 +15258,7 @@
         <v>1</v>
       </c>
       <c r="N217" t="n">
-        <v>10100100</v>
+        <v>101001001</v>
       </c>
     </row>
     <row r="218">
@@ -15365,7 +15365,7 @@
         <v>1</v>
       </c>
       <c r="N218" t="n">
-        <v>1101100</v>
+        <v>1100001</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/new_jobs(flags).xlsx
+++ b/Excel/new_jobs(flags).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N218"/>
+  <dimension ref="A1:O218"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,6 +499,11 @@
           <t>score</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>TZ</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -561,6 +566,11 @@
       <c r="N2" t="n">
         <v>1100001</v>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -623,6 +633,11 @@
       <c r="N3" t="n">
         <v>1001001.1</v>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -685,6 +700,11 @@
       <c r="N4" t="n">
         <v>1000001.1</v>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -747,6 +767,11 @@
       <c r="N5" t="n">
         <v>1001001</v>
       </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -809,6 +834,7 @@
       <c r="N6" t="n">
         <v>1001000</v>
       </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -871,6 +897,7 @@
       <c r="N7" t="n">
         <v>1001000</v>
       </c>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -933,6 +960,7 @@
       <c r="N8" t="n">
         <v>1000</v>
       </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -995,6 +1023,7 @@
       <c r="N9" t="n">
         <v>1</v>
       </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1057,6 +1086,7 @@
       <c r="N10" t="n">
         <v>1000</v>
       </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1119,6 +1149,7 @@
       <c r="N11" t="n">
         <v>1000001.01</v>
       </c>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1181,6 +1212,7 @@
       <c r="N12" t="n">
         <v>1000000.01</v>
       </c>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1243,6 +1275,7 @@
       <c r="N13" t="n">
         <v>1000000</v>
       </c>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1305,6 +1338,7 @@
       <c r="N14" t="n">
         <v>1100001.01</v>
       </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1367,6 +1401,7 @@
       <c r="N15" t="n">
         <v>10001000</v>
       </c>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1429,6 +1464,7 @@
       <c r="N16" t="n">
         <v>0</v>
       </c>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1491,6 +1527,7 @@
       <c r="N17" t="n">
         <v>1000101.1</v>
       </c>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1553,6 +1590,7 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1648,6 +1686,11 @@
       <c r="N19" t="n">
         <v>11100001</v>
       </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1742,6 +1785,11 @@
       <c r="N20" t="n">
         <v>1001001</v>
       </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1832,6 +1880,11 @@
       <c r="N21" t="n">
         <v>1000000</v>
       </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1894,6 +1947,7 @@
       <c r="N22" t="n">
         <v>100001000</v>
       </c>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1952,6 +2006,11 @@
       <c r="N23" t="n">
         <v>0</v>
       </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2006,6 +2065,7 @@
       <c r="N24" t="n">
         <v>10000000</v>
       </c>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2103,6 +2163,7 @@
       <c r="N25" t="n">
         <v>1000001</v>
       </c>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2161,6 +2222,7 @@
       <c r="N26" t="n">
         <v>0</v>
       </c>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2222,6 +2284,11 @@
       </c>
       <c r="N27" t="n">
         <v>1000001</v>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -2363,6 +2430,7 @@
       <c r="N28" t="n">
         <v>111001001</v>
       </c>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2460,6 +2528,7 @@
       <c r="N29" t="n">
         <v>1000001</v>
       </c>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2521,6 +2590,11 @@
       </c>
       <c r="N30" t="n">
         <v>0</v>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
       </c>
     </row>
     <row r="31">
@@ -2622,6 +2696,7 @@
       <c r="N31" t="n">
         <v>1</v>
       </c>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2723,6 +2798,11 @@
       <c r="N32" t="n">
         <v>1001001</v>
       </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2785,6 +2865,11 @@
       <c r="N33" t="n">
         <v>11010001</v>
       </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2846,6 +2931,11 @@
       </c>
       <c r="N34" t="n">
         <v>11010001</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -2951,6 +3041,7 @@
       <c r="N35" t="n">
         <v>100000001</v>
       </c>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3013,6 +3104,11 @@
       <c r="N36" t="n">
         <v>100001001</v>
       </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3074,6 +3170,11 @@
       </c>
       <c r="N37" t="n">
         <v>100001000</v>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
       </c>
     </row>
     <row r="38">
@@ -3178,6 +3279,7 @@
       <c r="N38" t="n">
         <v>1</v>
       </c>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3283,6 +3385,7 @@
       <c r="N39" t="n">
         <v>0</v>
       </c>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3385,6 +3488,7 @@
       <c r="N40" t="n">
         <v>1001</v>
       </c>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3488,6 +3592,7 @@
       <c r="N41" t="n">
         <v>1</v>
       </c>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3593,6 +3698,7 @@
       <c r="N42" t="n">
         <v>0</v>
       </c>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3698,6 +3804,7 @@
       <c r="N43" t="n">
         <v>0</v>
       </c>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3801,6 +3908,7 @@
       <c r="N44" t="n">
         <v>1</v>
       </c>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3902,6 +4010,7 @@
       <c r="N45" t="n">
         <v>1</v>
       </c>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3964,6 +4073,7 @@
       <c r="N46" t="n">
         <v>101100001.11</v>
       </c>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4026,6 +4136,7 @@
       <c r="N47" t="n">
         <v>1000001</v>
       </c>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4104,6 +4215,11 @@
       </c>
       <c r="N48" t="n">
         <v>1000001.01</v>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -4185,6 +4301,11 @@
       </c>
       <c r="N49" t="n">
         <v>1001001.11</v>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -4304,6 +4425,7 @@
       <c r="N50" t="n">
         <v>101000001</v>
       </c>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4405,6 +4527,11 @@
       <c r="N51" t="n">
         <v>11100001</v>
       </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4463,6 +4590,7 @@
       <c r="N52" t="n">
         <v>0</v>
       </c>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4521,6 +4649,7 @@
       <c r="N53" t="n">
         <v>10000000</v>
       </c>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4579,6 +4708,11 @@
       <c r="N54" t="n">
         <v>10000000</v>
       </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4637,6 +4771,7 @@
       <c r="N55" t="n">
         <v>0</v>
       </c>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4699,6 +4834,7 @@
       <c r="N56" t="n">
         <v>1</v>
       </c>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4761,6 +4897,7 @@
       <c r="N57" t="n">
         <v>1000001</v>
       </c>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4823,6 +4960,7 @@
       <c r="N58" t="n">
         <v>1</v>
       </c>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4885,6 +5023,7 @@
       <c r="N59" t="n">
         <v>1000001</v>
       </c>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4947,6 +5086,11 @@
       <c r="N60" t="n">
         <v>0</v>
       </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5009,6 +5153,11 @@
       <c r="N61" t="n">
         <v>1001001</v>
       </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5071,6 +5220,7 @@
       <c r="N62" t="n">
         <v>1000001</v>
       </c>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5133,6 +5283,7 @@
       <c r="N63" t="n">
         <v>1001001</v>
       </c>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5195,6 +5346,11 @@
       <c r="N64" t="n">
         <v>1001001</v>
       </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5257,6 +5413,11 @@
       <c r="N65" t="n">
         <v>1001001</v>
       </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5319,6 +5480,11 @@
       <c r="N66" t="n">
         <v>1101001</v>
       </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5381,6 +5547,11 @@
       <c r="N67" t="n">
         <v>0</v>
       </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5443,6 +5614,7 @@
       <c r="N68" t="n">
         <v>1000001</v>
       </c>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5505,6 +5677,11 @@
       <c r="N69" t="n">
         <v>1001001</v>
       </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5567,6 +5744,7 @@
       <c r="N70" t="n">
         <v>1010001</v>
       </c>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5629,6 +5807,11 @@
       <c r="N71" t="n">
         <v>1000000.1</v>
       </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5691,6 +5874,7 @@
       <c r="N72" t="n">
         <v>1001001</v>
       </c>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5753,6 +5937,11 @@
       <c r="N73" t="n">
         <v>1001001</v>
       </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5815,6 +6004,11 @@
       <c r="N74" t="n">
         <v>1000001</v>
       </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5877,6 +6071,11 @@
       <c r="N75" t="n">
         <v>1101001</v>
       </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5939,6 +6138,7 @@
       <c r="N76" t="n">
         <v>1</v>
       </c>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -6001,6 +6201,7 @@
       <c r="N77" t="n">
         <v>1000001.11</v>
       </c>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6063,6 +6264,7 @@
       <c r="N78" t="n">
         <v>1000001.11</v>
       </c>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6125,6 +6327,7 @@
       <c r="N79" t="n">
         <v>1000001.11</v>
       </c>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6187,6 +6390,7 @@
       <c r="N80" t="n">
         <v>11000001.11</v>
       </c>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6249,6 +6453,7 @@
       <c r="N81" t="n">
         <v>11000001.11</v>
       </c>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6311,6 +6516,7 @@
       <c r="N82" t="n">
         <v>1001001</v>
       </c>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6373,6 +6579,7 @@
       <c r="N83" t="n">
         <v>1001001</v>
       </c>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6435,6 +6642,7 @@
       <c r="N84" t="n">
         <v>1001001</v>
       </c>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6497,6 +6705,7 @@
       <c r="N85" t="n">
         <v>11010001</v>
       </c>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6559,6 +6768,7 @@
       <c r="N86" t="n">
         <v>11010001</v>
       </c>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6621,6 +6831,7 @@
       <c r="N87" t="n">
         <v>1001001</v>
       </c>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6683,6 +6894,7 @@
       <c r="N88" t="n">
         <v>1001001</v>
       </c>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6745,6 +6957,7 @@
       <c r="N89" t="n">
         <v>1001001</v>
       </c>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6807,6 +7020,7 @@
       <c r="N90" t="n">
         <v>1001001</v>
       </c>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6869,6 +7083,7 @@
       <c r="N91" t="n">
         <v>1001001</v>
       </c>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -6931,6 +7146,7 @@
       <c r="N92" t="n">
         <v>1001001</v>
       </c>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6993,6 +7209,7 @@
       <c r="N93" t="n">
         <v>1001001.01</v>
       </c>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7055,6 +7272,7 @@
       <c r="N94" t="n">
         <v>1001001.01</v>
       </c>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7117,6 +7335,7 @@
       <c r="N95" t="n">
         <v>1101000</v>
       </c>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7179,6 +7398,7 @@
       <c r="N96" t="n">
         <v>1101000</v>
       </c>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7241,6 +7461,7 @@
       <c r="N97" t="n">
         <v>1000001</v>
       </c>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7303,6 +7524,7 @@
       <c r="N98" t="n">
         <v>100001000</v>
       </c>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7365,6 +7587,7 @@
       <c r="N99" t="n">
         <v>100001000</v>
       </c>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7427,6 +7650,7 @@
       <c r="N100" t="n">
         <v>101001001</v>
       </c>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7489,6 +7713,7 @@
       <c r="N101" t="n">
         <v>101001101.1</v>
       </c>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7551,6 +7776,7 @@
       <c r="N102" t="n">
         <v>1001101.1</v>
       </c>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7613,6 +7839,7 @@
       <c r="N103" t="n">
         <v>101101001</v>
       </c>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7675,6 +7902,7 @@
       <c r="N104" t="n">
         <v>0</v>
       </c>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -7737,6 +7965,7 @@
       <c r="N105" t="n">
         <v>1001001</v>
       </c>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -7799,6 +8028,7 @@
       <c r="N106" t="n">
         <v>101001001</v>
       </c>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -7861,6 +8091,7 @@
       <c r="N107" t="n">
         <v>1001001</v>
       </c>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -7923,6 +8154,7 @@
       <c r="N108" t="n">
         <v>101001001</v>
       </c>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -7985,6 +8217,7 @@
       <c r="N109" t="n">
         <v>1001001</v>
       </c>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8047,6 +8280,7 @@
       <c r="N110" t="n">
         <v>101001001</v>
       </c>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8109,6 +8343,7 @@
       <c r="N111" t="n">
         <v>1101001</v>
       </c>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8171,6 +8406,7 @@
       <c r="N112" t="n">
         <v>101101001</v>
       </c>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8233,6 +8469,7 @@
       <c r="N113" t="n">
         <v>101001001</v>
       </c>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8295,6 +8532,7 @@
       <c r="N114" t="n">
         <v>1001001</v>
       </c>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8357,6 +8595,7 @@
       <c r="N115" t="n">
         <v>100000000.1</v>
       </c>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8419,6 +8658,7 @@
       <c r="N116" t="n">
         <v>1000001.1</v>
       </c>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8481,6 +8721,7 @@
       <c r="N117" t="n">
         <v>1000001.01</v>
       </c>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8543,6 +8784,7 @@
       <c r="N118" t="n">
         <v>10000000</v>
       </c>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -8605,6 +8847,7 @@
       <c r="N119" t="n">
         <v>1110001.11</v>
       </c>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -8667,6 +8910,7 @@
       <c r="N120" t="n">
         <v>1101001.11</v>
       </c>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -8729,6 +8973,7 @@
       <c r="N121" t="n">
         <v>1110001.11</v>
       </c>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -8791,6 +9036,7 @@
       <c r="N122" t="n">
         <v>1101001.11</v>
       </c>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -8853,6 +9099,7 @@
       <c r="N123" t="n">
         <v>1110001.11</v>
       </c>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -8915,6 +9162,7 @@
       <c r="N124" t="n">
         <v>11101001.01</v>
       </c>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -8977,6 +9225,7 @@
       <c r="N125" t="n">
         <v>1001001</v>
       </c>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9039,6 +9288,7 @@
       <c r="N126" t="n">
         <v>1000</v>
       </c>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9101,6 +9351,7 @@
       <c r="N127" t="n">
         <v>1001000</v>
       </c>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9163,6 +9414,7 @@
       <c r="N128" t="n">
         <v>1000000</v>
       </c>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9225,6 +9477,7 @@
       <c r="N129" t="n">
         <v>1101001</v>
       </c>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9287,6 +9540,7 @@
       <c r="N130" t="n">
         <v>1001001</v>
       </c>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9349,6 +9603,7 @@
       <c r="N131" t="n">
         <v>1101001</v>
       </c>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9411,6 +9666,7 @@
       <c r="N132" t="n">
         <v>1001001.1</v>
       </c>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9473,6 +9729,7 @@
       <c r="N133" t="n">
         <v>1001.1</v>
       </c>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9535,6 +9792,7 @@
       <c r="N134" t="n">
         <v>1001001.1</v>
       </c>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9597,6 +9855,7 @@
       <c r="N135" t="n">
         <v>1001001</v>
       </c>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9659,6 +9918,7 @@
       <c r="N136" t="n">
         <v>1001001</v>
       </c>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9721,6 +9981,7 @@
       <c r="N137" t="n">
         <v>1001001.1</v>
       </c>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -9783,6 +10044,7 @@
       <c r="N138" t="n">
         <v>1001000</v>
       </c>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -9845,6 +10107,7 @@
       <c r="N139" t="n">
         <v>1001001</v>
       </c>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -9907,6 +10170,7 @@
       <c r="N140" t="n">
         <v>11001001</v>
       </c>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -9969,6 +10233,7 @@
       <c r="N141" t="n">
         <v>1001000</v>
       </c>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10031,6 +10296,7 @@
       <c r="N142" t="n">
         <v>1001001</v>
       </c>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10093,6 +10359,7 @@
       <c r="N143" t="n">
         <v>1110001.1</v>
       </c>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10155,6 +10422,7 @@
       <c r="N144" t="n">
         <v>11001001</v>
       </c>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10217,6 +10485,7 @@
       <c r="N145" t="n">
         <v>1001000</v>
       </c>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -10279,6 +10548,7 @@
       <c r="N146" t="n">
         <v>1001001</v>
       </c>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -10341,6 +10611,7 @@
       <c r="N147" t="n">
         <v>1001001.01</v>
       </c>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -10403,6 +10674,7 @@
       <c r="N148" t="n">
         <v>1001001</v>
       </c>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -10465,6 +10737,7 @@
       <c r="N149" t="n">
         <v>1000001</v>
       </c>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -10527,6 +10800,7 @@
       <c r="N150" t="n">
         <v>1001001</v>
       </c>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -10589,6 +10863,7 @@
       <c r="N151" t="n">
         <v>1001001</v>
       </c>
+      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -10651,6 +10926,7 @@
       <c r="N152" t="n">
         <v>1000001.01</v>
       </c>
+      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -10713,6 +10989,7 @@
       <c r="N153" t="n">
         <v>1000001.01</v>
       </c>
+      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -10775,6 +11052,7 @@
       <c r="N154" t="n">
         <v>1001001.1</v>
       </c>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -10837,6 +11115,7 @@
       <c r="N155" t="n">
         <v>1001001.1</v>
       </c>
+      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -10899,6 +11178,7 @@
       <c r="N156" t="n">
         <v>1000001.1</v>
       </c>
+      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -10961,6 +11241,7 @@
       <c r="N157" t="n">
         <v>1000001.1</v>
       </c>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -11023,6 +11304,11 @@
       <c r="N158" t="n">
         <v>101001001</v>
       </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -11085,6 +11371,11 @@
       <c r="N159" t="n">
         <v>101000001</v>
       </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -11147,6 +11438,7 @@
       <c r="N160" t="n">
         <v>0</v>
       </c>
+      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -11209,6 +11501,7 @@
       <c r="N161" t="n">
         <v>101001001</v>
       </c>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -11311,6 +11604,7 @@
       <c r="N162" t="n">
         <v>1000000</v>
       </c>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -11373,6 +11667,7 @@
       <c r="N163" t="n">
         <v>11000001.01</v>
       </c>
+      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11435,6 +11730,7 @@
       <c r="N164" t="n">
         <v>11000001.01</v>
       </c>
+      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11497,6 +11793,7 @@
       <c r="N165" t="n">
         <v>11001001.01</v>
       </c>
+      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -11559,6 +11856,7 @@
       <c r="N166" t="n">
         <v>11001001.01</v>
       </c>
+      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11621,6 +11919,7 @@
       <c r="N167" t="n">
         <v>1101001</v>
       </c>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -11709,6 +12008,11 @@
       </c>
       <c r="N168" t="n">
         <v>100001000.1</v>
+      </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -11833,6 +12137,7 @@
       <c r="N169" t="n">
         <v>101000000</v>
       </c>
+      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -11959,6 +12264,7 @@
       <c r="N170" t="n">
         <v>100001000</v>
       </c>
+      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -12078,6 +12384,7 @@
       <c r="N171" t="n">
         <v>101101001</v>
       </c>
+      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12200,6 +12507,7 @@
       <c r="N172" t="n">
         <v>101001001</v>
       </c>
+      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -12279,6 +12587,7 @@
       <c r="N173" t="n">
         <v>11000000</v>
       </c>
+      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -12341,6 +12650,7 @@
       <c r="N174" t="n">
         <v>101001000</v>
       </c>
+      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -12441,6 +12751,11 @@
       <c r="N175" t="n">
         <v>1001001</v>
       </c>
+      <c r="O175" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -12503,6 +12818,7 @@
       <c r="N176" t="n">
         <v>101000000</v>
       </c>
+      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -12565,6 +12881,7 @@
       <c r="N177" t="n">
         <v>10001100.1</v>
       </c>
+      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -12627,6 +12944,7 @@
       <c r="N178" t="n">
         <v>1001001.1</v>
       </c>
+      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -12689,6 +13007,7 @@
       <c r="N179" t="n">
         <v>1001001</v>
       </c>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -12751,6 +13070,7 @@
       <c r="N180" t="n">
         <v>1000001</v>
       </c>
+      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -12813,6 +13133,7 @@
       <c r="N181" t="n">
         <v>1000001</v>
       </c>
+      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -12875,6 +13196,7 @@
       <c r="N182" t="n">
         <v>1001001</v>
       </c>
+      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -12937,6 +13259,7 @@
       <c r="N183" t="n">
         <v>1100001.11</v>
       </c>
+      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -12999,6 +13322,7 @@
       <c r="N184" t="n">
         <v>0.11</v>
       </c>
+      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -13061,6 +13385,7 @@
       <c r="N185" t="n">
         <v>0</v>
       </c>
+      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -13123,6 +13448,7 @@
       <c r="N186" t="n">
         <v>1100001.11</v>
       </c>
+      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13185,6 +13511,7 @@
       <c r="N187" t="n">
         <v>11000001</v>
       </c>
+      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13247,6 +13574,7 @@
       <c r="N188" t="n">
         <v>1100001</v>
       </c>
+      <c r="O188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13309,6 +13637,7 @@
       <c r="N189" t="n">
         <v>1001001</v>
       </c>
+      <c r="O189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13371,6 +13700,7 @@
       <c r="N190" t="n">
         <v>0</v>
       </c>
+      <c r="O190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13433,6 +13763,7 @@
       <c r="N191" t="n">
         <v>100000001</v>
       </c>
+      <c r="O191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -13599,6 +13930,7 @@
       <c r="N192" t="n">
         <v>101000000</v>
       </c>
+      <c r="O192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -13710,6 +14042,7 @@
       <c r="N193" t="n">
         <v>111100001</v>
       </c>
+      <c r="O193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -13772,6 +14105,7 @@
       <c r="N194" t="n">
         <v>1000</v>
       </c>
+      <c r="O194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -13834,6 +14168,7 @@
       <c r="N195" t="n">
         <v>1000000</v>
       </c>
+      <c r="O195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -13896,6 +14231,7 @@
       <c r="N196" t="n">
         <v>1001001</v>
       </c>
+      <c r="O196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -13958,6 +14294,7 @@
       <c r="N197" t="n">
         <v>1001001</v>
       </c>
+      <c r="O197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -14020,6 +14357,7 @@
       <c r="N198" t="n">
         <v>1100000</v>
       </c>
+      <c r="O198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -14082,6 +14420,7 @@
       <c r="N199" t="n">
         <v>101001001.11</v>
       </c>
+      <c r="O199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -14144,6 +14483,7 @@
       <c r="N200" t="n">
         <v>0</v>
       </c>
+      <c r="O200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -14206,6 +14546,7 @@
       <c r="N201" t="n">
         <v>111100001</v>
       </c>
+      <c r="O201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -14268,6 +14609,7 @@
       <c r="N202" t="n">
         <v>1000000</v>
       </c>
+      <c r="O202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -14330,6 +14672,7 @@
       <c r="N203" t="n">
         <v>0</v>
       </c>
+      <c r="O203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -14392,6 +14735,7 @@
       <c r="N204" t="n">
         <v>1000001</v>
       </c>
+      <c r="O204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14454,6 +14798,7 @@
       <c r="N205" t="n">
         <v>101001001.01</v>
       </c>
+      <c r="O205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14516,6 +14861,7 @@
       <c r="N206" t="n">
         <v>101100001.01</v>
       </c>
+      <c r="O206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -14578,6 +14924,7 @@
       <c r="N207" t="n">
         <v>100000001</v>
       </c>
+      <c r="O207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -14640,6 +14987,7 @@
       <c r="N208" t="n">
         <v>100000001</v>
       </c>
+      <c r="O208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -14702,6 +15050,7 @@
       <c r="N209" t="n">
         <v>101001001.1</v>
       </c>
+      <c r="O209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -14764,6 +15113,7 @@
       <c r="N210" t="n">
         <v>111101001</v>
       </c>
+      <c r="O210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -14826,6 +15176,7 @@
       <c r="N211" t="n">
         <v>111101001</v>
       </c>
+      <c r="O211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -14888,6 +15239,7 @@
       <c r="N212" t="n">
         <v>111101001</v>
       </c>
+      <c r="O212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -14950,6 +15302,7 @@
       <c r="N213" t="n">
         <v>100000001</v>
       </c>
+      <c r="O213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15012,6 +15365,7 @@
       <c r="N214" t="n">
         <v>1001001.1</v>
       </c>
+      <c r="O214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15074,6 +15428,7 @@
       <c r="N215" t="n">
         <v>1001001.01</v>
       </c>
+      <c r="O215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -15136,6 +15491,7 @@
       <c r="N216" t="n">
         <v>1001001.01</v>
       </c>
+      <c r="O216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -15260,6 +15616,11 @@
       <c r="N217" t="n">
         <v>101001001</v>
       </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -15367,6 +15728,11 @@
       <c r="N218" t="n">
         <v>1100001</v>
       </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Excel/new_jobs(flags).xlsx
+++ b/Excel/new_jobs(flags).xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
@@ -635,7 +635,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
@@ -702,7 +702,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>ET</t>
         </is>
       </c>
     </row>
@@ -960,7 +960,11 @@
       <c r="N8" t="n">
         <v>1000</v>
       </c>
-      <c r="O8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1947,7 +1951,11 @@
       <c r="N22" t="n">
         <v>100001000</v>
       </c>
-      <c r="O22" t="inlineStr"/>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4073,7 +4081,11 @@
       <c r="N46" t="n">
         <v>101100001.11</v>
       </c>
-      <c r="O46" t="inlineStr"/>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -10170,7 +10182,11 @@
       <c r="N140" t="n">
         <v>11001001</v>
       </c>
-      <c r="O140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -11667,7 +11683,11 @@
       <c r="N163" t="n">
         <v>11000001.01</v>
       </c>
-      <c r="O163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -11793,7 +11813,11 @@
       <c r="N165" t="n">
         <v>11001001.01</v>
       </c>
-      <c r="O165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -12137,7 +12161,11 @@
       <c r="N169" t="n">
         <v>101000000</v>
       </c>
-      <c r="O169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -12264,7 +12292,11 @@
       <c r="N170" t="n">
         <v>100001000</v>
       </c>
-      <c r="O170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -13700,7 +13732,11 @@
       <c r="N190" t="n">
         <v>0</v>
       </c>
-      <c r="O190" t="inlineStr"/>
+      <c r="O190" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -13763,7 +13799,11 @@
       <c r="N191" t="n">
         <v>100000001</v>
       </c>
-      <c r="O191" t="inlineStr"/>
+      <c r="O191" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -14105,7 +14145,11 @@
       <c r="N194" t="n">
         <v>1000</v>
       </c>
-      <c r="O194" t="inlineStr"/>
+      <c r="O194" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -14168,7 +14212,11 @@
       <c r="N195" t="n">
         <v>1000000</v>
       </c>
-      <c r="O195" t="inlineStr"/>
+      <c r="O195" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -14231,7 +14279,11 @@
       <c r="N196" t="n">
         <v>1001001</v>
       </c>
-      <c r="O196" t="inlineStr"/>
+      <c r="O196" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -14735,7 +14787,11 @@
       <c r="N204" t="n">
         <v>1000001</v>
       </c>
-      <c r="O204" t="inlineStr"/>
+      <c r="O204" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -14798,7 +14854,11 @@
       <c r="N205" t="n">
         <v>101001001.01</v>
       </c>
-      <c r="O205" t="inlineStr"/>
+      <c r="O205" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -14924,7 +14984,11 @@
       <c r="N207" t="n">
         <v>100000001</v>
       </c>
-      <c r="O207" t="inlineStr"/>
+      <c r="O207" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -15239,7 +15303,11 @@
       <c r="N212" t="n">
         <v>111101001</v>
       </c>
-      <c r="O212" t="inlineStr"/>
+      <c r="O212" t="inlineStr">
+        <is>
+          <t>ET</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">

--- a/Excel/new_jobs(flags).xlsx
+++ b/Excel/new_jobs(flags).xlsx
@@ -834,7 +834,11 @@
       <c r="N6" t="n">
         <v>1001000</v>
       </c>
-      <c r="O6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14472,7 +14476,11 @@
       <c r="N199" t="n">
         <v>101001001.11</v>
       </c>
-      <c r="O199" t="inlineStr"/>
+      <c r="O199" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">

--- a/Excel/new_jobs(flags).xlsx
+++ b/Excel/new_jobs(flags).xlsx
@@ -6217,7 +6217,11 @@
       <c r="N77" t="n">
         <v>1000001.11</v>
       </c>
-      <c r="O77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -8737,7 +8741,11 @@
       <c r="N117" t="n">
         <v>1000001.01</v>
       </c>
-      <c r="O117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -9241,7 +9249,11 @@
       <c r="N125" t="n">
         <v>1001001</v>
       </c>
-      <c r="O125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -9304,7 +9316,11 @@
       <c r="N126" t="n">
         <v>1000</v>
       </c>
-      <c r="O126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -9367,7 +9383,11 @@
       <c r="N127" t="n">
         <v>1001000</v>
       </c>
-      <c r="O127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -9430,7 +9450,11 @@
       <c r="N128" t="n">
         <v>1000000</v>
       </c>
-      <c r="O128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -9493,7 +9517,11 @@
       <c r="N129" t="n">
         <v>1101001</v>
       </c>
-      <c r="O129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -9556,7 +9584,11 @@
       <c r="N130" t="n">
         <v>1001001</v>
       </c>
-      <c r="O130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -9619,7 +9651,11 @@
       <c r="N131" t="n">
         <v>1101001</v>
       </c>
-      <c r="O131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -9682,7 +9718,11 @@
       <c r="N132" t="n">
         <v>1001001.1</v>
       </c>
-      <c r="O132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -9745,7 +9785,11 @@
       <c r="N133" t="n">
         <v>1001.1</v>
       </c>
-      <c r="O133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -9808,7 +9852,11 @@
       <c r="N134" t="n">
         <v>1001001.1</v>
       </c>
-      <c r="O134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -9871,7 +9919,11 @@
       <c r="N135" t="n">
         <v>1001001</v>
       </c>
-      <c r="O135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -9934,7 +9986,11 @@
       <c r="N136" t="n">
         <v>1001001</v>
       </c>
-      <c r="O136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -9997,7 +10053,11 @@
       <c r="N137" t="n">
         <v>1001001.1</v>
       </c>
-      <c r="O137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -10060,7 +10120,11 @@
       <c r="N138" t="n">
         <v>1001000</v>
       </c>
-      <c r="O138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -10123,7 +10187,11 @@
       <c r="N139" t="n">
         <v>1001001</v>
       </c>
-      <c r="O139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -10253,7 +10321,11 @@
       <c r="N141" t="n">
         <v>1001000</v>
       </c>
-      <c r="O141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -10316,7 +10388,11 @@
       <c r="N142" t="n">
         <v>1001001</v>
       </c>
-      <c r="O142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -10379,7 +10455,11 @@
       <c r="N143" t="n">
         <v>1110001.1</v>
       </c>
-      <c r="O143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -10442,7 +10522,11 @@
       <c r="N144" t="n">
         <v>11001001</v>
       </c>
-      <c r="O144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -10757,7 +10841,11 @@
       <c r="N149" t="n">
         <v>1000001</v>
       </c>
-      <c r="O149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -11754,7 +11842,11 @@
       <c r="N164" t="n">
         <v>11000001.01</v>
       </c>
-      <c r="O164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -11884,7 +11976,11 @@
       <c r="N166" t="n">
         <v>11001001.01</v>
       </c>
-      <c r="O166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -11947,7 +12043,11 @@
       <c r="N167" t="n">
         <v>1101001</v>
       </c>
-      <c r="O167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -12420,7 +12520,11 @@
       <c r="N171" t="n">
         <v>101101001</v>
       </c>
-      <c r="O171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -12543,7 +12647,11 @@
       <c r="N172" t="n">
         <v>101001001</v>
       </c>
-      <c r="O172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -13295,7 +13403,11 @@
       <c r="N183" t="n">
         <v>1100001.11</v>
       </c>
-      <c r="O183" t="inlineStr"/>
+      <c r="O183" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -13358,7 +13470,11 @@
       <c r="N184" t="n">
         <v>0.11</v>
       </c>
-      <c r="O184" t="inlineStr"/>
+      <c r="O184" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -13484,7 +13600,11 @@
       <c r="N186" t="n">
         <v>1100001.11</v>
       </c>
-      <c r="O186" t="inlineStr"/>
+      <c r="O186" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -13547,7 +13667,11 @@
       <c r="N187" t="n">
         <v>11000001</v>
       </c>
-      <c r="O187" t="inlineStr"/>
+      <c r="O187" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -13610,7 +13734,11 @@
       <c r="N188" t="n">
         <v>1100001</v>
       </c>
-      <c r="O188" t="inlineStr"/>
+      <c r="O188" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -13673,7 +13801,11 @@
       <c r="N189" t="n">
         <v>1001001</v>
       </c>
-      <c r="O189" t="inlineStr"/>
+      <c r="O189" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -13974,7 +14106,11 @@
       <c r="N192" t="n">
         <v>101000000</v>
       </c>
-      <c r="O192" t="inlineStr"/>
+      <c r="O192" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -14086,7 +14222,11 @@
       <c r="N193" t="n">
         <v>111100001</v>
       </c>
-      <c r="O193" t="inlineStr"/>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -14543,7 +14683,11 @@
       <c r="N200" t="n">
         <v>0</v>
       </c>
-      <c r="O200" t="inlineStr"/>
+      <c r="O200" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -14929,7 +15073,11 @@
       <c r="N206" t="n">
         <v>101100001.01</v>
       </c>
-      <c r="O206" t="inlineStr"/>
+      <c r="O206" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -15059,7 +15207,11 @@
       <c r="N208" t="n">
         <v>100000001</v>
       </c>
-      <c r="O208" t="inlineStr"/>
+      <c r="O208" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -15122,7 +15274,11 @@
       <c r="N209" t="n">
         <v>101001001.1</v>
       </c>
-      <c r="O209" t="inlineStr"/>
+      <c r="O209" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -15248,7 +15404,11 @@
       <c r="N211" t="n">
         <v>111101001</v>
       </c>
-      <c r="O211" t="inlineStr"/>
+      <c r="O211" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -15378,7 +15538,11 @@
       <c r="N213" t="n">
         <v>100000001</v>
       </c>
-      <c r="O213" t="inlineStr"/>
+      <c r="O213" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -15441,7 +15605,11 @@
       <c r="N214" t="n">
         <v>1001001.1</v>
       </c>
-      <c r="O214" t="inlineStr"/>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -15504,7 +15672,11 @@
       <c r="N215" t="n">
         <v>1001001.01</v>
       </c>
-      <c r="O215" t="inlineStr"/>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">

--- a/Excel/new_jobs(flags).xlsx
+++ b/Excel/new_jobs(flags).xlsx
@@ -15341,7 +15341,11 @@
       <c r="N210" t="n">
         <v>111101001</v>
       </c>
-      <c r="O210" t="inlineStr"/>
+      <c r="O210" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
